--- a/Field Layout.xlsx
+++ b/Field Layout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://horizontal-my.sharepoint.com/personal/dpanchal_horizontal_com/Documents/CursorAutomation/ProcurementClassification/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_F25DC773A252ABDACC104832F11D406A5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA97DC98-F243-4463-9551-F2CD6DC28805}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC104832F11D406A5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8A7D19F-CB69-40D9-B1CC-367942B94B57}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10575" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,9 +69,6 @@
     <t>Mobile</t>
   </si>
   <si>
-    <t>Portfolio</t>
-  </si>
-  <si>
     <t>Lead Source</t>
   </si>
   <si>
@@ -81,12 +78,6 @@
     <t>Procurement Classification</t>
   </si>
   <si>
-    <t xml:space="preserve">Procurement Sector </t>
-  </si>
-  <si>
-    <t>Procurement Channel</t>
-  </si>
-  <si>
     <t>Request Type</t>
   </si>
   <si>
@@ -99,9 +90,6 @@
     <t>Estimated Budget</t>
   </si>
   <si>
-    <t>Current Supplier</t>
-  </si>
-  <si>
     <t>Decision Maker Identified</t>
   </si>
   <si>
@@ -154,6 +142,18 @@
   </si>
   <si>
     <t>Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sector </t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>Division</t>
+  </si>
+  <si>
+    <t>Supplier</t>
   </si>
 </sst>
 </file>
@@ -287,24 +287,12 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -312,6 +300,18 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -600,198 +600,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="B1" s="11"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="1"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="11"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B14" s="11"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="3"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="3" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="B19" s="11"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B22" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B23" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B24" s="13"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B25" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="3" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="B26" s="11"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="10"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="12"/>
+      <c r="B27" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="6">
